--- a/attendance/2026-05-10.xlsx
+++ b/attendance/2026-05-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>07:58:11</t>
+          <t>12:16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>nguyen_tuan_hoang</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>12:16:15</t>
         </is>
       </c>
     </row>
